--- a/source/Last-time-buy models.xlsx
+++ b/source/Last-time-buy models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jhonedcel_nolasco\Desktop\Test Pilot - HP Pricelist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBF644B9-6001-492B-A905-2AF8B4CCDB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255CD3DB-AA1D-43D9-82DC-C6A2A4A37186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{BABCA01C-3E54-4E5F-A717-A0B8A32B6D48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{BABCA01C-3E54-4E5F-A717-A0B8A32B6D48}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
   <si>
     <t>Tagging</t>
   </si>
@@ -214,21 +214,6 @@
   </si>
   <si>
     <t>Premium - Pav</t>
-  </si>
-  <si>
-    <t>HP-NB A46T3PA PAV PLUS 14-EW1009TU U5</t>
-  </si>
-  <si>
-    <t>U5-125H 16GB 5X OB 512GB INTEL ARC 14 WQXGA MB</t>
-  </si>
-  <si>
-    <t>PHP 61,060.00</t>
-  </si>
-  <si>
-    <t>PHP 76,990.00</t>
-  </si>
-  <si>
-    <t>PHP 59,228</t>
   </si>
   <si>
     <t>HP-NB B49W8PA PAVILION 16-AF0063TU U5</t>
@@ -322,20 +307,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,10 +636,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F810D1C2-82DB-47F6-A496-FB657E1A41FB}">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O68"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="51.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +675,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -699,13 +695,13 @@
         <v>12</v>
       </c>
       <c r="G2" s="2">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="114" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -731,7 +727,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -751,13 +747,13 @@
         <v>24</v>
       </c>
       <c r="G4" s="2">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -777,13 +773,13 @@
         <v>29</v>
       </c>
       <c r="G5" s="2">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
@@ -809,7 +805,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
@@ -829,13 +825,13 @@
         <v>40</v>
       </c>
       <c r="G7" s="2">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>36</v>
       </c>
@@ -855,13 +851,13 @@
         <v>45</v>
       </c>
       <c r="G8" s="2">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
@@ -881,13 +877,13 @@
         <v>51</v>
       </c>
       <c r="G9" s="2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
@@ -907,89 +903,71 @@
         <v>57</v>
       </c>
       <c r="G10" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A11" s="4" t="s">
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="4">
-        <v>432115035713</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="B11" s="2">
+        <v>432115035987</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G11" s="2">
-        <v>27</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="4">
+        <v>432115035989</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="2">
-        <v>432115035987</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G12" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="4">
-        <v>432115035989</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="2">
-        <v>6</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>73</v>
-      </c>
+    <row r="52" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O52" s="5"/>
+    </row>
+    <row r="68" spans="15:15" x14ac:dyDescent="0.25">
+      <c r="O68" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
